--- a/order_forms/043_sports_league_flag_printing_order_form--order_forms.xlsx
+++ b/order_forms/043_sports_league_flag_printing_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'custom',_'value':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Custom', 'value': 'custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'stock',_'value':_'stock'}</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Stock', 'value': 'stock'}</t>
+          <t>Stock</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flag',_'value':_'flag'}</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flag', 'value': 'flag'}</t>
+          <t>Flag</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'banner',_'value':_'banner'}</t>
+          <t>banner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Banner', 'value': 'banner'}</t>
+          <t>Banner</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'banners',_'value':_'banners'}</t>
+          <t>banners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Banners', 'value': 'banners'}</t>
+          <t>Banners</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flag',_'value':_'flag'}</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flag', 'value': 'flag'}</t>
+          <t>Flag</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'number',_'value':_'number'}</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Number', 'value': 'number'}</t>
+          <t>Number</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'logo',_'value':_'logo'}</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Logo', 'value': 'logo'}</t>
+          <t>Logo</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monochrome',_'value':_'monochrome'}</t>
+          <t>monochrome</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monochrome', 'value': 'monochrome'}</t>
+          <t>Monochrome</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'multicolor',_'value':_'multicolor'}</t>
+          <t>multicolor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Multicolor', 'value': 'multicolor'}</t>
+          <t>Multicolor</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'payment',_'value':_'payment'}</t>
+          <t>payment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Payment', 'value': 'payment'}</t>
+          <t>Payment</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'deposit',_'value':_'deposit'}</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Deposit', 'value': 'deposit'}</t>
+          <t>Deposit</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small',_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small', 'value': 'small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'large',_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Large', 'value': 'large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'extra_large',_'value':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Extra Large', 'value': 'extra_large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Single', 'value': 'single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dual',_'value':_'dual'}</t>
+          <t>dual</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dual', 'value': 'dual'}</t>
+          <t>Dual</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
